--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -826,49 +826,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110146378</v>
+        <v>110353286</v>
       </c>
       <c r="B3" t="n">
-        <v>108220</v>
+        <v>106457</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>231446</v>
+        <v>231235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hallandsfibbla</t>
+          <t>Narrklibbfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hieracium subterdentatum</t>
+          <t>Hieracium chlorodes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Johanss. &amp; Sam.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dahlst.) Dahlst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -876,17 +867,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tönnersjö, 150 m SSV Bygdegården, vägkant, Hl</t>
+          <t>Tönnersjö, 150 m SSV Bygdegården, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379993</v>
+        <v>379992.5271192961</v>
       </c>
       <c r="R3" t="n">
-        <v>6277938</v>
+        <v>6277938.192996203</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -908,24 +899,24 @@
           <t>Tönnersjö</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>N-Hal-1673</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2023-06-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sannolikt beror det låga antalet på den långvariga torkan</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,6 +933,12 @@
           <t>Gräsrik vägkant mot blandskog</t>
         </is>
       </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -953,18 +950,14 @@
           <t>Kjell Georgson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110353286</v>
+        <v>109711725</v>
       </c>
       <c r="B4" t="n">
-        <v>106457</v>
+        <v>56534</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -973,46 +966,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>231235</v>
+        <v>102118</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Narrklibbfibbla</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hieracium chlorodes</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dahlst.) Dahlst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tönnersjö, 150 m SSV Bygdegården, Hl</t>
+          <t>Perstorp, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379992.5271192961</v>
+        <v>379675</v>
       </c>
       <c r="R4" t="n">
-        <v>6277938.192996203</v>
+        <v>6277583</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1036,22 +1036,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1063,153 +1063,18 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Gräsrik vägkant mot blandskog</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Kjell Georgson</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kjell Georgson</t>
+          <t>Göran Ericson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kjell Georgson</t>
+          <t>Göran Ericson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>109711725</v>
-      </c>
-      <c r="B5" t="n">
-        <v>56534</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>102118</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Nattskärra</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Caprimulgus europaeus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Perstorp, Hl</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>379675</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6277583</v>
-      </c>
-      <c r="S5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Halmstad</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Tönnersjö</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>23:06</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>23:06</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Göran Ericson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Göran Ericson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -957,12 +957,7 @@
         <v>109711725</v>
       </c>
       <c r="B4" t="n">
-        <v>56534</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -957,7 +957,7 @@
         <v>109711725</v>
       </c>
       <c r="B4" t="n">
-        <v>57453</v>
+        <v>57454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -957,7 +957,7 @@
         <v>109711725</v>
       </c>
       <c r="B4" t="n">
-        <v>57454</v>
+        <v>57458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -957,7 +957,7 @@
         <v>109711725</v>
       </c>
       <c r="B4" t="n">
-        <v>57458</v>
+        <v>57459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1071,6 +1071,134 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126584217</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108891</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>231446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hallandsfibbla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hieracium subterdentatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Johanss. &amp; Sam.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tönnersjö, 150 m SSV Bygdegården, vägkant, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>379998</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6277934</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tönnersjö</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>N-Hal-1673</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vägkanten klippt, några rosetter återstod, endast en blomställning kvar</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Magnusson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Erik Magnusson, Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -1076,7 +1076,7 @@
         <v>126584217</v>
       </c>
       <c r="B5" t="n">
-        <v>108891</v>
+        <v>108966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -1076,7 +1076,7 @@
         <v>126584217</v>
       </c>
       <c r="B5" t="n">
-        <v>108966</v>
+        <v>108972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>102207207</v>
       </c>
       <c r="B2" t="n">
-        <v>106680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>109292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379992.5271192961</v>
+        <v>379998</v>
       </c>
       <c r="R2" t="n">
-        <v>6277938.192996203</v>
+        <v>6277934</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,19 +762,9 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -826,40 +811,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110353286</v>
+        <v>110146378</v>
       </c>
       <c r="B3" t="n">
-        <v>106457</v>
+        <v>108220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>231235</v>
+        <v>231446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Narrklibbfibbla</t>
+          <t>Hallandsfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hieracium chlorodes</t>
+          <t>Hieracium subterdentatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dahlst.) Dahlst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Johanss. &amp; Sam.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -867,17 +861,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tönnersjö, 150 m SSV Bygdegården, Hl</t>
+          <t>Tönnersjö, 150 m SSV Bygdegården, vägkant, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379992.5271192961</v>
+        <v>379993</v>
       </c>
       <c r="R3" t="n">
-        <v>6277938.192996203</v>
+        <v>6277938</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,24 +893,24 @@
           <t>Tönnersjö</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>N-Hal-1673</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2023-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sannolikt beror det låga antalet på den långvariga torkan</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,12 +927,6 @@
           <t>Gräsrik vägkant mot blandskog</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Kjell Georgson</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -950,64 +938,66 @@
           <t>Kjell Georgson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109711725</v>
+        <v>110353286</v>
       </c>
       <c r="B4" t="n">
-        <v>57459</v>
+        <v>106457</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102118</v>
+        <v>231235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Narrklibbfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Hieracium chlorodes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Dahlst.) Dahlst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Perstorp, Hl</t>
+          <t>Tönnersjö, 150 m SSV Bygdegården, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379675</v>
+        <v>379992.5271192961</v>
       </c>
       <c r="R4" t="n">
-        <v>6277583</v>
+        <v>6277938.192996203</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1031,22 +1021,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:06</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:06</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,79 +1048,86 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gräsrik vägkant mot blandskog</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ericson</t>
+          <t>Kjell Georgson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ericson</t>
+          <t>Kjell Georgson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126584217</v>
+        <v>109711725</v>
       </c>
       <c r="B5" t="n">
-        <v>108972</v>
+        <v>57459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>231446</v>
+        <v>102118</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hallandsfibbla</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hieracium subterdentatum</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Johanss. &amp; Sam.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tönnersjö, 150 m SSV Bygdegården, vägkant, Hl</t>
+          <t>Perstorp, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379998</v>
+        <v>379675</v>
       </c>
       <c r="R5" t="n">
-        <v>6277934</v>
+        <v>6277583</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1152,24 +1149,24 @@
           <t>Tönnersjö</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>N-Hal-1673</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>23:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vägkanten klippt, några rosetter återstod, endast en blomställning kvar</t>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>23:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,26 +1175,21 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Magnusson</t>
+          <t>Göran Ericson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Magnusson, Kjell Georgson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>102207207</v>
       </c>
       <c r="B2" t="n">
-        <v>109292</v>
+        <v>109295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>102207207</v>
       </c>
       <c r="B2" t="n">
-        <v>109295</v>
+        <v>109324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>102207207</v>
       </c>
       <c r="B2" t="n">
-        <v>109324</v>
+        <v>109336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>102207207</v>
       </c>
       <c r="B2" t="n">
-        <v>109336</v>
+        <v>109337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>102207207</v>
       </c>
       <c r="B2" t="n">
-        <v>109337</v>
+        <v>109342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>102207207</v>
       </c>
       <c r="B2" t="n">
-        <v>109342</v>
+        <v>109346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>102207207</v>
       </c>
       <c r="B2" t="n">
-        <v>109346</v>
+        <v>109348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>102207207</v>
       </c>
       <c r="B2" t="n">
-        <v>109348</v>
+        <v>109358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -1077,7 +1077,7 @@
         <v>109711725</v>
       </c>
       <c r="B5" t="n">
-        <v>57459</v>
+        <v>57759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -1077,7 +1077,7 @@
         <v>109711725</v>
       </c>
       <c r="B5" t="n">
-        <v>57759</v>
+        <v>57766</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -1077,7 +1077,7 @@
         <v>109711725</v>
       </c>
       <c r="B5" t="n">
-        <v>57766</v>
+        <v>57776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102207207</v>
+        <v>101064275</v>
       </c>
       <c r="B2" t="n">
-        <v>109358</v>
+        <v>57776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>231446</v>
+        <v>102118</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hallandsfibbla</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hieracium subterdentatum</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Johanss. &amp; Sam.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tönnersjö, 150 m SSV Bygdegården, vägkant, Hl</t>
+          <t>Halmstad, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379998</v>
+        <v>379678</v>
       </c>
       <c r="R2" t="n">
-        <v>6277934</v>
+        <v>6277582</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,24 +749,24 @@
           <t>Tönnersjö</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>N-Hal-1673</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-05-22</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Medobservatör Bitte Georgson</t>
+          <t>2022-05-22</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,97 +778,75 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Gräsrik vägkant mot blandskog</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Kjell Georgson</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kjell Georgson</t>
+          <t>Robin Mårtensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kjell Georgson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Robin Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110146378</v>
+        <v>109711725</v>
       </c>
       <c r="B3" t="n">
-        <v>108220</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>231446</v>
+        <v>102118</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hallandsfibbla</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hieracium subterdentatum</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Johanss. &amp; Sam.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tönnersjö, 150 m SSV Bygdegården, vägkant, Hl</t>
+          <t>Perstorp, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379993</v>
+        <v>379675</v>
       </c>
       <c r="R3" t="n">
-        <v>6277938</v>
+        <v>6277583</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -893,24 +868,24 @@
           <t>Tönnersjö</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>N-Hal-1673</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>23:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sannolikt beror det låga antalet på den långvariga torkan</t>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>23:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,83 +896,76 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Gräsrik vägkant mot blandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kjell Georgson</t>
+          <t>Göran Ericson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kjell Georgson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110353286</v>
+        <v>109767334</v>
       </c>
       <c r="B4" t="n">
-        <v>106457</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>231235</v>
+        <v>102118</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Narrklibbfibbla</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hieracium chlorodes</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dahlst.) Dahlst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tönnersjö, 150 m SSV Bygdegården, Hl</t>
+          <t>Perstorp Skogstomten, Halmstad, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379992.5271192961</v>
+        <v>379628</v>
       </c>
       <c r="R4" t="n">
-        <v>6277938.192996203</v>
+        <v>6277527</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,22 +989,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-06-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-06-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,86 +1016,79 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Gräsrik vägkant mot blandskog</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Kjell Georgson</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kjell Georgson</t>
+          <t>Annelie Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kjell Georgson</t>
+          <t>Annelie Larsson, Elin Lundgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109711725</v>
+        <v>88489232</v>
       </c>
       <c r="B5" t="n">
-        <v>57776</v>
+        <v>110078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102118</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Perstorp, Hl</t>
+          <t>Tönnersjövägen, 750 m NO Perstorpskrysset, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>379675</v>
+        <v>379422</v>
       </c>
       <c r="R5" t="n">
-        <v>6277583</v>
+        <v>6277305</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1149,24 +1110,24 @@
           <t>Tönnersjö</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Arkiv-N-Hal-0874</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>23:06</t>
+          <t>2020-05-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>23:06</t>
+          <t>2020-05-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,21 +1136,275 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ericson</t>
+          <t>Lars-Erik Magnusson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ericson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Lars-Erik Magnusson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110353286</v>
+      </c>
+      <c r="B6" t="n">
+        <v>109564</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>231235</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Narrklibbfibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hieracium chlorodes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dahlst.) Dahlst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tönnersjö, 150 m SSV Bygdegården, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>379993</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6277938</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tönnersjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gräsrik vägkant mot blandskog</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102207207</v>
+      </c>
+      <c r="B7" t="n">
+        <v>109784</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>231446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hallandsfibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hieracium subterdentatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Johanss. &amp; Sam.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tönnersjö, 150 m SSV Bygdegården, vägkant, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>379998</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6277934</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tönnersjö</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>N-Hal-1673</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Medobservatör Bitte Georgson</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gräsrik vägkant mot blandskog</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kjell Georgson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30890-2022 artfynd.xlsx
+++ b/artfynd/A 30890-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101064275</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109711725</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109767334</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88489232</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1269,6 +1294,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110353286</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1405,8 +1435,21 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102207207</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>